--- a/outputs/Tahminlenen_Talep.xlsx
+++ b/outputs/Tahminlenen_Talep.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,8 +439,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46153</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -461,8 +459,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46154</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -479,8 +479,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46155</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -497,8 +499,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46156</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -515,8 +519,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46157</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -533,8 +539,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46158</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -551,8 +559,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46159</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -569,8 +579,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46153</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -587,8 +599,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46154</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -605,8 +619,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46155</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -623,8 +639,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46156</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -641,8 +659,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46157</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -659,8 +679,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46158</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -677,8 +699,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46159</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -695,8 +719,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46153</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -713,8 +739,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46154</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -731,8 +759,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46155</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -749,8 +779,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46156</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -767,8 +799,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46157</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -785,8 +819,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46158</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -803,8 +839,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46159</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -821,8 +859,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46153</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -839,8 +879,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46154</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -857,8 +899,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46155</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -875,8 +919,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46156</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -893,8 +939,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>46157</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -911,8 +959,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>46158</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -929,8 +979,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>46159</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -947,8 +999,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>46153</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -965,8 +1019,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>46154</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -983,8 +1039,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>46155</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1001,8 +1059,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>46156</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1019,8 +1079,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46157</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1037,8 +1099,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46158</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1055,8 +1119,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46159</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1073,8 +1139,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46153</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1091,8 +1159,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46154</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1109,8 +1179,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46155</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1127,8 +1199,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46156</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1145,8 +1219,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46157</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1163,8 +1239,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>46158</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1181,8 +1259,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>46159</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1199,8 +1279,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>46153</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1217,8 +1299,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>46154</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1235,8 +1319,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>46155</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1253,8 +1339,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46156</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1271,8 +1359,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46157</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1289,8 +1379,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>46158</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1307,8 +1399,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>46159</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1325,8 +1419,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>46153</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1343,8 +1439,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46154</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1361,8 +1459,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>46155</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1379,8 +1479,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>46156</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1397,8 +1499,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>46157</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1415,8 +1519,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>46158</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1433,8 +1539,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>46159</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1451,8 +1559,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>46153</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1469,8 +1579,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>46154</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1487,8 +1599,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>46155</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1505,8 +1619,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>46156</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1523,8 +1639,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>46157</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1541,8 +1659,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>46158</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1559,8 +1679,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>46159</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1577,8 +1699,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>46153</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1595,8 +1719,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>46154</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1613,8 +1739,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>46155</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -1631,8 +1759,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>46156</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1649,8 +1779,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>46157</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1667,8 +1799,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>46158</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -1685,8 +1819,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>46159</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -1703,8 +1839,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>46153</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -1721,8 +1859,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>46154</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -1739,8 +1879,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>46155</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -1757,8 +1899,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>46156</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -1775,8 +1919,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>46157</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -1793,8 +1939,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>46158</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1811,8 +1959,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>46159</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -1829,8 +1979,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>46153</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -1847,8 +1999,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>46154</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -1865,8 +2019,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>46155</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -1883,8 +2039,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>46156</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -1901,8 +2059,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>46157</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -1919,8 +2079,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>46158</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -1937,8 +2099,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>46159</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -1955,8 +2119,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>46153</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -1973,8 +2139,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>46154</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -1991,8 +2159,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>46155</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2009,8 +2179,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>46156</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2027,8 +2199,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>46157</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2045,8 +2219,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>46158</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2063,8 +2239,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>46159</v>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2081,8 +2259,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>46153</v>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -2099,8 +2279,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>46154</v>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -2117,8 +2299,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>46155</v>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -2135,8 +2319,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>46156</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2153,8 +2339,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>46157</v>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -2171,8 +2359,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>46158</v>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -2189,8 +2379,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>46159</v>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -2207,8 +2399,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>46153</v>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -2225,8 +2419,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>46154</v>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -2243,8 +2439,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>46155</v>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -2261,8 +2459,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>46156</v>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -2279,8 +2479,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>46157</v>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -2297,8 +2499,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
-        <v>46158</v>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -2315,8 +2519,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>46159</v>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -2333,8 +2539,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>46153</v>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -2351,8 +2559,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>46154</v>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -2369,8 +2579,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
-        <v>46155</v>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -2387,8 +2599,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>46156</v>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -2405,8 +2619,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>46157</v>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -2423,8 +2639,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
-        <v>46158</v>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -2441,8 +2659,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>46159</v>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -2459,8 +2679,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
-        <v>46153</v>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -2477,8 +2699,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
-        <v>46154</v>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -2495,8 +2719,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>46155</v>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -2513,8 +2739,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
-        <v>46156</v>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -2531,8 +2759,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
-        <v>46157</v>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -2549,8 +2779,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>46158</v>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -2567,8 +2799,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
-        <v>46159</v>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -2585,8 +2819,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
-        <v>46153</v>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -2603,8 +2839,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>46154</v>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -2621,8 +2859,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
-        <v>46155</v>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -2639,8 +2879,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>46156</v>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -2657,8 +2899,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>46157</v>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -2675,8 +2919,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>46158</v>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -2693,8 +2939,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>46159</v>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -2711,8 +2959,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
-        <v>46153</v>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -2729,8 +2979,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
-        <v>46154</v>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -2747,8 +2999,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
-        <v>46155</v>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -2765,8 +3019,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>46156</v>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -2783,8 +3039,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
-        <v>46157</v>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -2801,8 +3059,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
-        <v>46158</v>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -2819,8 +3079,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
-        <v>46159</v>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -2837,8 +3099,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
-        <v>46153</v>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -2855,8 +3119,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
-        <v>46154</v>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -2873,8 +3139,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
-        <v>46155</v>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -2891,8 +3159,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
-        <v>46156</v>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -2909,8 +3179,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
-        <v>46157</v>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -2927,8 +3199,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
-        <v>46158</v>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -2945,8 +3219,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
-        <v>46159</v>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -2963,8 +3239,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
-        <v>46153</v>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -2981,8 +3259,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
-        <v>46154</v>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -2999,8 +3279,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
-        <v>46155</v>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -3017,8 +3299,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
-        <v>46156</v>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -3035,8 +3319,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
-        <v>46157</v>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -3053,8 +3339,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
-        <v>46158</v>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -3071,8 +3359,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
-        <v>46159</v>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -3089,8 +3379,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
-        <v>46153</v>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -3107,8 +3399,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
-        <v>46154</v>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -3125,8 +3419,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
-        <v>46155</v>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -3143,8 +3439,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
-        <v>46156</v>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -3161,8 +3459,10 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
-        <v>46157</v>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -3179,8 +3479,10 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
-        <v>46158</v>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -3197,8 +3499,10 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
-        <v>46159</v>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -3215,8 +3519,10 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
-        <v>46153</v>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -3233,8 +3539,10 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
-        <v>46154</v>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -3251,8 +3559,10 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
-        <v>46155</v>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -3269,8 +3579,10 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
-        <v>46156</v>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -3287,8 +3599,10 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
-        <v>46157</v>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -3305,8 +3619,10 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
-        <v>46158</v>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -3323,8 +3639,10 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
-        <v>46159</v>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -3341,8 +3659,10 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
-        <v>46153</v>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -3359,8 +3679,10 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
-        <v>46154</v>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -3377,8 +3699,10 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
-        <v>46155</v>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -3395,8 +3719,10 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
-        <v>46156</v>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -3413,8 +3739,10 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
-        <v>46157</v>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -3431,8 +3759,10 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
-        <v>46158</v>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -3449,8 +3779,10 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
-        <v>46159</v>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -3467,8 +3799,10 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
-        <v>46153</v>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -3485,8 +3819,10 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
-        <v>46154</v>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -3503,8 +3839,10 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
-        <v>46155</v>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -3521,8 +3859,10 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
-        <v>46156</v>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -3539,8 +3879,10 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
-        <v>46157</v>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -3557,8 +3899,10 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
-        <v>46158</v>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -3575,8 +3919,10 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
-        <v>46159</v>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -3593,8 +3939,10 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
-        <v>46153</v>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -3611,8 +3959,10 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
-        <v>46154</v>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -3629,8 +3979,10 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
-        <v>46155</v>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -3647,8 +3999,10 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
-        <v>46156</v>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -3665,8 +4019,10 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
-        <v>46157</v>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -3683,8 +4039,10 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
-        <v>46158</v>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -3701,8 +4059,10 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
-        <v>46159</v>
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -3719,8 +4079,10 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
-        <v>46153</v>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -3737,8 +4099,10 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
-        <v>46154</v>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -3755,8 +4119,10 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
-        <v>46155</v>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -3773,8 +4139,10 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
-        <v>46156</v>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -3791,8 +4159,10 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
-        <v>46157</v>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -3809,8 +4179,10 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
-        <v>46158</v>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -3827,8 +4199,10 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
-        <v>46159</v>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -3845,8 +4219,10 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
-        <v>46153</v>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -3863,8 +4239,10 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
-        <v>46154</v>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -3881,8 +4259,10 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
-        <v>46155</v>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -3899,8 +4279,10 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
-        <v>46156</v>
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -3917,8 +4299,10 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
-        <v>46157</v>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -3935,8 +4319,10 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
-        <v>46158</v>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -3953,8 +4339,10 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
-        <v>46159</v>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -3971,8 +4359,10 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
-        <v>46153</v>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -3989,8 +4379,10 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
-        <v>46154</v>
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -4007,8 +4399,10 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
-        <v>46155</v>
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -4025,8 +4419,10 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
-        <v>46156</v>
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -4043,8 +4439,10 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
-        <v>46157</v>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -4061,8 +4459,10 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
-        <v>46158</v>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -4079,8 +4479,10 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
-        <v>46159</v>
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -4097,8 +4499,10 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
-        <v>46153</v>
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -4115,8 +4519,10 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
-        <v>46154</v>
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -4133,8 +4539,10 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
-        <v>46155</v>
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -4151,8 +4559,10 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
-        <v>46156</v>
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -4169,8 +4579,10 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
-        <v>46157</v>
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -4187,8 +4599,10 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
-        <v>46158</v>
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -4205,8 +4619,10 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
-        <v>46159</v>
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -4223,8 +4639,10 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
-        <v>46153</v>
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -4241,8 +4659,10 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
-        <v>46154</v>
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -4259,8 +4679,10 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
-        <v>46155</v>
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -4277,8 +4699,10 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
-        <v>46156</v>
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -4295,8 +4719,10 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
-        <v>46157</v>
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -4313,8 +4739,10 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
-        <v>46158</v>
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -4331,8 +4759,10 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
-        <v>46159</v>
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -4349,8 +4779,10 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
-        <v>46153</v>
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -4367,8 +4799,10 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
-        <v>46154</v>
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -4385,8 +4819,10 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
-        <v>46155</v>
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -4403,8 +4839,10 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
-        <v>46156</v>
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -4421,8 +4859,10 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
-        <v>46157</v>
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -4439,8 +4879,10 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
-        <v>46158</v>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -4457,8 +4899,10 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
-        <v>46159</v>
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -4475,8 +4919,10 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
-        <v>46153</v>
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -4493,8 +4939,10 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
-        <v>46154</v>
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -4511,8 +4959,10 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
-        <v>46155</v>
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -4529,8 +4979,10 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
-        <v>46156</v>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -4547,8 +4999,10 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
-        <v>46157</v>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -4565,8 +5019,10 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
-        <v>46158</v>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -4583,8 +5039,10 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
-        <v>46159</v>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -4601,8 +5059,10 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
-        <v>46153</v>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -4619,8 +5079,10 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
-        <v>46154</v>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -4637,8 +5099,10 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
-        <v>46155</v>
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -4655,8 +5119,10 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
-        <v>46156</v>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -4673,8 +5139,10 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
-        <v>46157</v>
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -4691,8 +5159,10 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
-        <v>46158</v>
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -4709,8 +5179,10 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
-        <v>46159</v>
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -4727,8 +5199,10 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
-        <v>46153</v>
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -4745,8 +5219,10 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
-        <v>46154</v>
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -4763,8 +5239,10 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
-        <v>46155</v>
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -4781,8 +5259,10 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
-        <v>46156</v>
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -4799,8 +5279,10 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
-        <v>46157</v>
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -4817,8 +5299,10 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
-        <v>46158</v>
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -4835,8 +5319,10 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
-        <v>46159</v>
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -4853,8 +5339,10 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
-        <v>46153</v>
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -4871,8 +5359,10 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
-        <v>46154</v>
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -4889,8 +5379,10 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
-        <v>46155</v>
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -4907,8 +5399,10 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
-        <v>46156</v>
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -4925,8 +5419,10 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
-        <v>46157</v>
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -4943,8 +5439,10 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
-        <v>46158</v>
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -4961,8 +5459,10 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46159</v>
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -4979,8 +5479,10 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
-        <v>46153</v>
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -4997,8 +5499,10 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
-        <v>46154</v>
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -5015,8 +5519,10 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
-        <v>46155</v>
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -5033,8 +5539,10 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
-        <v>46156</v>
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -5051,8 +5559,10 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
-        <v>46157</v>
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -5069,8 +5579,10 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
-        <v>46158</v>
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -5087,8 +5599,10 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
-        <v>46159</v>
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -5105,8 +5619,10 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
-        <v>46153</v>
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -5123,8 +5639,10 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
-        <v>46154</v>
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -5141,8 +5659,10 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
-        <v>46155</v>
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -5159,8 +5679,10 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
-        <v>46156</v>
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -5177,8 +5699,10 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
-        <v>46157</v>
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -5195,8 +5719,10 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
-        <v>46158</v>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -5213,8 +5739,10 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
-        <v>46159</v>
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -5231,8 +5759,10 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
-        <v>46153</v>
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -5249,8 +5779,10 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
-        <v>46154</v>
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -5267,8 +5799,10 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
-        <v>46155</v>
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -5285,8 +5819,10 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
-        <v>46156</v>
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -5303,8 +5839,10 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
-        <v>46157</v>
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -5321,8 +5859,10 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
-        <v>46158</v>
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -5339,8 +5879,10 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
-        <v>46159</v>
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -5357,8 +5899,10 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
-        <v>46153</v>
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -5375,8 +5919,10 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
-        <v>46154</v>
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -5393,8 +5939,10 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
-        <v>46155</v>
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -5411,8 +5959,10 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
-        <v>46156</v>
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -5429,8 +5979,10 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
-        <v>46157</v>
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -5447,8 +5999,10 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
-        <v>46158</v>
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -5465,8 +6019,10 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
-        <v>46159</v>
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -5483,8 +6039,10 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
-        <v>46153</v>
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -5501,8 +6059,10 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
-        <v>46154</v>
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -5519,8 +6079,10 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
-        <v>46155</v>
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -5537,8 +6099,10 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
-        <v>46156</v>
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -5555,8 +6119,10 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
-        <v>46157</v>
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -5573,8 +6139,10 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
-        <v>46158</v>
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -5591,8 +6159,10 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
-        <v>46159</v>
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -5609,8 +6179,10 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
-        <v>46153</v>
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -5627,8 +6199,10 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
-        <v>46154</v>
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -5645,8 +6219,10 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
-        <v>46155</v>
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -5663,8 +6239,10 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
-        <v>46156</v>
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -5681,8 +6259,10 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
-        <v>46157</v>
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -5699,8 +6279,10 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
-        <v>46158</v>
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -5717,8 +6299,10 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
-        <v>46159</v>
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -5735,8 +6319,10 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
-        <v>46153</v>
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -5753,8 +6339,10 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
-        <v>46154</v>
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -5771,8 +6359,10 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
-        <v>46155</v>
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -5789,8 +6379,10 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
-        <v>46156</v>
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -5807,8 +6399,10 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
-        <v>46157</v>
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -5825,8 +6419,10 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
-        <v>46158</v>
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -5843,8 +6439,10 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
-        <v>46159</v>
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -5861,8 +6459,10 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
-        <v>46153</v>
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -5879,8 +6479,10 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
-        <v>46154</v>
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -5897,8 +6499,10 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
-        <v>46155</v>
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -5915,8 +6519,10 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
-        <v>46156</v>
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -5933,8 +6539,10 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
-        <v>46157</v>
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -5951,8 +6559,10 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
-        <v>46158</v>
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -5969,8 +6579,10 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
-        <v>46159</v>
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -5987,8 +6599,10 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
-        <v>46153</v>
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -6005,8 +6619,10 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
-        <v>46154</v>
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -6023,8 +6639,10 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
-        <v>46155</v>
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -6041,8 +6659,10 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
-        <v>46156</v>
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -6059,8 +6679,10 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
-        <v>46157</v>
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -6077,8 +6699,10 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
-        <v>46158</v>
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -6095,8 +6719,10 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
-        <v>46159</v>
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -6113,8 +6739,10 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
-        <v>46153</v>
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -6131,8 +6759,10 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
-        <v>46154</v>
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -6149,8 +6779,10 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
-        <v>46155</v>
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -6167,8 +6799,10 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
-        <v>46156</v>
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -6185,8 +6819,10 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
-        <v>46157</v>
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -6203,8 +6839,10 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
-        <v>46158</v>
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -6221,8 +6859,10 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
-        <v>46159</v>
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -6239,8 +6879,10 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
-        <v>46153</v>
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -6257,8 +6899,10 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
-        <v>46154</v>
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -6275,8 +6919,10 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
-        <v>46155</v>
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
@@ -6293,8 +6939,10 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
-        <v>46156</v>
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -6311,8 +6959,10 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
-        <v>46157</v>
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
@@ -6329,8 +6979,10 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
-        <v>46158</v>
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -6347,8 +6999,10 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
-        <v>46159</v>
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -6365,8 +7019,10 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
-        <v>46153</v>
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -6383,8 +7039,10 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
-        <v>46154</v>
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -6401,8 +7059,10 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
-        <v>46155</v>
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -6419,8 +7079,10 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
-        <v>46156</v>
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -6437,8 +7099,10 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
-        <v>46157</v>
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
@@ -6455,8 +7119,10 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
-        <v>46158</v>
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
@@ -6473,8 +7139,10 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
-        <v>46159</v>
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -6491,8 +7159,10 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
-        <v>46153</v>
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -6509,8 +7179,10 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
-        <v>46154</v>
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
@@ -6527,8 +7199,10 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
-        <v>46155</v>
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
@@ -6545,8 +7219,10 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
-        <v>46156</v>
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -6563,8 +7239,10 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
-        <v>46157</v>
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
@@ -6581,8 +7259,10 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
-        <v>46158</v>
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
@@ -6599,8 +7279,10 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
-        <v>46159</v>
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -6617,8 +7299,10 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
-        <v>46153</v>
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -6635,8 +7319,10 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
-        <v>46154</v>
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -6653,8 +7339,10 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
-        <v>46155</v>
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -6671,8 +7359,10 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
-        <v>46156</v>
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
@@ -6689,8 +7379,10 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
-        <v>46157</v>
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -6707,8 +7399,10 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
-        <v>46158</v>
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -6725,8 +7419,10 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
-        <v>46159</v>
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -6743,8 +7439,10 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
-        <v>46153</v>
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -6761,8 +7459,10 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
-        <v>46154</v>
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -6779,8 +7479,10 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
-        <v>46155</v>
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -6797,8 +7499,10 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
-        <v>46156</v>
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -6815,8 +7519,10 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
-        <v>46157</v>
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -6833,8 +7539,10 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
-        <v>46158</v>
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -6851,8 +7559,10 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
-        <v>46159</v>
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -6869,8 +7579,10 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
-        <v>46153</v>
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -6887,8 +7599,10 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
-        <v>46154</v>
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -6905,8 +7619,10 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
-        <v>46155</v>
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -6923,8 +7639,10 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
-        <v>46156</v>
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -6941,8 +7659,10 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
-        <v>46157</v>
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -6959,8 +7679,10 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
-        <v>46158</v>
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -6977,8 +7699,10 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
-        <v>46159</v>
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -6995,8 +7719,10 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
-        <v>46153</v>
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -7013,8 +7739,10 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
-        <v>46154</v>
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -7031,8 +7759,10 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
-        <v>46155</v>
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -7049,8 +7779,10 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
-        <v>46156</v>
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -7067,8 +7799,10 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
-        <v>46157</v>
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -7085,8 +7819,10 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
-        <v>46158</v>
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -7103,8 +7839,10 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
-        <v>46159</v>
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -7121,8 +7859,10 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
-        <v>46153</v>
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -7139,8 +7879,10 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
-        <v>46154</v>
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -7157,8 +7899,10 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
-        <v>46155</v>
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -7175,8 +7919,10 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
-        <v>46156</v>
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -7193,8 +7939,10 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>46157</v>
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -7211,8 +7959,10 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>46158</v>
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -7229,8 +7979,10 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>46159</v>
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -7247,8 +7999,10 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
-        <v>46153</v>
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -7265,8 +8019,10 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
-        <v>46154</v>
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -7283,8 +8039,10 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
-        <v>46155</v>
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -7301,8 +8059,10 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
-        <v>46156</v>
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -7319,8 +8079,10 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
-        <v>46157</v>
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -7337,8 +8099,10 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
-        <v>46158</v>
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -7355,8 +8119,10 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
-        <v>46159</v>
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -7373,8 +8139,10 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
-        <v>46153</v>
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -7391,8 +8159,10 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
-        <v>46154</v>
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -7409,8 +8179,10 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
-        <v>46155</v>
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -7427,8 +8199,10 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
-        <v>46156</v>
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -7445,8 +8219,10 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
-        <v>46157</v>
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -7463,8 +8239,10 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
-        <v>46158</v>
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -7481,8 +8259,10 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
-        <v>46159</v>
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -7499,8 +8279,10 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
-        <v>46153</v>
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -7517,8 +8299,10 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
-        <v>46154</v>
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -7535,8 +8319,10 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
-        <v>46155</v>
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -7553,8 +8339,10 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
-        <v>46156</v>
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -7571,8 +8359,10 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
-        <v>46157</v>
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -7589,8 +8379,10 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
-        <v>46158</v>
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -7607,8 +8399,10 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
-        <v>46159</v>
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -7625,8 +8419,10 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
-        <v>46153</v>
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -7643,8 +8439,10 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
-        <v>46154</v>
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -7661,8 +8459,10 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
-        <v>46155</v>
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -7679,8 +8479,10 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
-        <v>46156</v>
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -7697,8 +8499,10 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
-        <v>46157</v>
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
@@ -7715,8 +8519,10 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
-        <v>46158</v>
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -7733,8 +8539,10 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
-        <v>46159</v>
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
@@ -7751,8 +8559,10 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
-        <v>46153</v>
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -7769,8 +8579,10 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
-        <v>46154</v>
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
@@ -7787,8 +8599,10 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
-        <v>46155</v>
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -7805,8 +8619,10 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
-        <v>46156</v>
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -7823,8 +8639,10 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
-        <v>46157</v>
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -7841,8 +8659,10 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
-        <v>46158</v>
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -7859,8 +8679,10 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
-        <v>46159</v>
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -7877,8 +8699,10 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
-        <v>46153</v>
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -7895,8 +8719,10 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
-        <v>46154</v>
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -7913,8 +8739,10 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
-        <v>46155</v>
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -7931,8 +8759,10 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
-        <v>46156</v>
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
@@ -7949,8 +8779,10 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
-        <v>46157</v>
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -7967,8 +8799,10 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
-        <v>46158</v>
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
@@ -7985,8 +8819,10 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
-        <v>46159</v>
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
@@ -8003,8 +8839,10 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
-        <v>46153</v>
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
@@ -8021,8 +8859,10 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
-        <v>46154</v>
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
@@ -8039,8 +8879,10 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
-        <v>46155</v>
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
@@ -8057,8 +8899,10 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
-        <v>46156</v>
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -8075,8 +8919,10 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
-        <v>46157</v>
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
@@ -8093,8 +8939,10 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
-        <v>46158</v>
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -8111,8 +8959,10 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
-        <v>46159</v>
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -8129,8 +8979,10 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
-        <v>46153</v>
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
@@ -8147,8 +8999,10 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
-        <v>46154</v>
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -8165,8 +9019,10 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
-        <v>46155</v>
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -8183,8 +9039,10 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
-        <v>46156</v>
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
@@ -8201,8 +9059,10 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
-        <v>46157</v>
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
@@ -8219,8 +9079,10 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
-        <v>46158</v>
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
@@ -8237,8 +9099,10 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
-        <v>46159</v>
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -8255,8 +9119,10 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
-        <v>46153</v>
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -8273,8 +9139,10 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
-        <v>46154</v>
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -8291,8 +9159,10 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
-        <v>46155</v>
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
@@ -8309,8 +9179,10 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
-        <v>46156</v>
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -8327,8 +9199,10 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
-        <v>46157</v>
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
@@ -8345,8 +9219,10 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
-        <v>46158</v>
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
@@ -8363,8 +9239,10 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
-        <v>46159</v>
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
@@ -8381,8 +9259,10 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
-        <v>46153</v>
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
@@ -8399,8 +9279,10 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
-        <v>46154</v>
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
@@ -8417,8 +9299,10 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
-        <v>46155</v>
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -8435,8 +9319,10 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
-        <v>46156</v>
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -8453,8 +9339,10 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
-        <v>46157</v>
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -8471,8 +9359,10 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
-        <v>46158</v>
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -8489,8 +9379,10 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
-        <v>46159</v>
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -8507,8 +9399,10 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
-        <v>46153</v>
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -8525,8 +9419,10 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
-        <v>46154</v>
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -8543,8 +9439,10 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
-        <v>46155</v>
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -8561,8 +9459,10 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
-        <v>46156</v>
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -8579,8 +9479,10 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
-        <v>46157</v>
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -8597,8 +9499,10 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
-        <v>46158</v>
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -8615,8 +9519,10 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
-        <v>46159</v>
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -8633,8 +9539,10 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
-        <v>46153</v>
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -8651,8 +9559,10 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
-        <v>46154</v>
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -8669,8 +9579,10 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
-        <v>46155</v>
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -8687,8 +9599,10 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
-        <v>46156</v>
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -8705,8 +9619,10 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
-        <v>46157</v>
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -8723,8 +9639,10 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
-        <v>46158</v>
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -8741,8 +9659,10 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
-        <v>46159</v>
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -8759,8 +9679,10 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
-        <v>46153</v>
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -8777,8 +9699,10 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
-        <v>46154</v>
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -8795,8 +9719,10 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
-        <v>46155</v>
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -8813,8 +9739,10 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
-        <v>46156</v>
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -8831,8 +9759,10 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
-        <v>46157</v>
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -8849,8 +9779,10 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
-        <v>46158</v>
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -8867,8 +9799,10 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
-        <v>46159</v>
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -8885,8 +9819,10 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
-        <v>46153</v>
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -8903,8 +9839,10 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
-        <v>46154</v>
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -8921,8 +9859,10 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
-        <v>46155</v>
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -8939,8 +9879,10 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
-        <v>46156</v>
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -8957,8 +9899,10 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
-        <v>46157</v>
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -8975,8 +9919,10 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
-        <v>46158</v>
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -8993,8 +9939,10 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
-        <v>46159</v>
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -9011,8 +9959,10 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
-        <v>46153</v>
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -9029,8 +9979,10 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
-        <v>46154</v>
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -9047,8 +9999,10 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
-        <v>46155</v>
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -9065,8 +10019,10 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
-        <v>46156</v>
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -9083,8 +10039,10 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
-        <v>46157</v>
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -9101,8 +10059,10 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
-        <v>46158</v>
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -9119,8 +10079,10 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
-        <v>46159</v>
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -9137,8 +10099,10 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
-        <v>46153</v>
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -9155,8 +10119,10 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
-        <v>46154</v>
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -9173,8 +10139,10 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
-        <v>46155</v>
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -9191,8 +10159,10 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
-        <v>46156</v>
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -9209,8 +10179,10 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
-        <v>46157</v>
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -9227,8 +10199,10 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
-        <v>46158</v>
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -9245,8 +10219,10 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
-        <v>46159</v>
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -9263,8 +10239,10 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
-        <v>46153</v>
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -9281,8 +10259,10 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
-        <v>46154</v>
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -9299,8 +10279,10 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
-        <v>46155</v>
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -9317,8 +10299,10 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
-        <v>46156</v>
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -9335,8 +10319,10 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
-        <v>46157</v>
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -9353,8 +10339,10 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
-        <v>46158</v>
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -9371,8 +10359,10 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
-        <v>46159</v>
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -9389,8 +10379,10 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
-        <v>46153</v>
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -9407,8 +10399,10 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
-        <v>46154</v>
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -9425,8 +10419,10 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
-        <v>46155</v>
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -9443,8 +10439,10 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
-        <v>46156</v>
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -9461,8 +10459,10 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
-        <v>46157</v>
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -9479,8 +10479,10 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
-        <v>46158</v>
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -9497,8 +10499,10 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
-        <v>46159</v>
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -9515,8 +10519,10 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
-        <v>46153</v>
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -9533,8 +10539,10 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
-        <v>46154</v>
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -9551,8 +10559,10 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
-        <v>46155</v>
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -9569,8 +10579,10 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
-        <v>46156</v>
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -9587,8 +10599,10 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
-        <v>46157</v>
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -9605,8 +10619,10 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
-        <v>46158</v>
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -9623,8 +10639,10 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
-        <v>46159</v>
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -9641,8 +10659,10 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
-        <v>46153</v>
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -9659,8 +10679,10 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
-        <v>46154</v>
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -9677,8 +10699,10 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
-        <v>46155</v>
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -9695,8 +10719,10 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
-        <v>46156</v>
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -9713,8 +10739,10 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
-        <v>46157</v>
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -9731,8 +10759,10 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
-        <v>46158</v>
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -9749,8 +10779,10 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
-        <v>46159</v>
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -9767,8 +10799,10 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
-        <v>46153</v>
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -9785,8 +10819,10 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
-        <v>46154</v>
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -9803,8 +10839,10 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
-        <v>46155</v>
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -9821,8 +10859,10 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
-        <v>46156</v>
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -9839,8 +10879,10 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
-        <v>46157</v>
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -9857,8 +10899,10 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
-        <v>46158</v>
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -9875,8 +10919,10 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
-        <v>46159</v>
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -9893,8 +10939,10 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
-        <v>46153</v>
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -9911,8 +10959,10 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
-        <v>46154</v>
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -9929,8 +10979,10 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
-        <v>46155</v>
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -9947,8 +10999,10 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
-        <v>46156</v>
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -9965,8 +11019,10 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
-        <v>46157</v>
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -9983,8 +11039,10 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
-        <v>46158</v>
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -10001,8 +11059,10 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
-        <v>46159</v>
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -10019,8 +11079,10 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
-        <v>46153</v>
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -10037,8 +11099,10 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
-        <v>46154</v>
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -10055,8 +11119,10 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
-        <v>46155</v>
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -10073,8 +11139,10 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
-        <v>46156</v>
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -10091,8 +11159,10 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
-        <v>46157</v>
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -10109,8 +11179,10 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
-        <v>46158</v>
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -10127,8 +11199,10 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
-        <v>46159</v>
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -10145,8 +11219,10 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
-        <v>46153</v>
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -10163,8 +11239,10 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
-        <v>46154</v>
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -10181,8 +11259,10 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
-        <v>46155</v>
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -10199,8 +11279,10 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
-        <v>46156</v>
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -10217,8 +11299,10 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
-        <v>46157</v>
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -10235,8 +11319,10 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
-        <v>46158</v>
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -10253,8 +11339,10 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
-        <v>46159</v>
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -10271,8 +11359,10 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
-        <v>46153</v>
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -10289,8 +11379,10 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
-        <v>46154</v>
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -10307,8 +11399,10 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
-        <v>46155</v>
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -10325,8 +11419,10 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
-        <v>46156</v>
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -10343,8 +11439,10 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
-        <v>46157</v>
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -10361,8 +11459,10 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
-        <v>46158</v>
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -10379,8 +11479,10 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
-        <v>46159</v>
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -10397,8 +11499,10 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
-        <v>46153</v>
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
@@ -10415,8 +11519,10 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
-        <v>46154</v>
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
@@ -10433,8 +11539,10 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
-        <v>46155</v>
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
@@ -10451,8 +11559,10 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
-        <v>46156</v>
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
@@ -10469,8 +11579,10 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
-        <v>46157</v>
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
@@ -10487,8 +11599,10 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
-        <v>46158</v>
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
@@ -10505,8 +11619,10 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
-        <v>46159</v>
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -10523,8 +11639,10 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
-        <v>46153</v>
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -10541,8 +11659,10 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
-        <v>46154</v>
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -10559,8 +11679,10 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
-        <v>46155</v>
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
@@ -10577,8 +11699,10 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
-        <v>46156</v>
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
@@ -10595,8 +11719,10 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
-        <v>46157</v>
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
@@ -10613,8 +11739,10 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
-        <v>46158</v>
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
@@ -10631,8 +11759,10 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
-        <v>46159</v>
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
@@ -10649,8 +11779,10 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
-        <v>46153</v>
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
@@ -10667,8 +11799,10 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
-        <v>46154</v>
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
@@ -10685,8 +11819,10 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
-        <v>46155</v>
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
@@ -10703,8 +11839,10 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
-        <v>46156</v>
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
@@ -10721,8 +11859,10 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
-        <v>46157</v>
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -10739,8 +11879,10 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
-        <v>46158</v>
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
@@ -10757,8 +11899,10 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
-        <v>46159</v>
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -10775,8 +11919,10 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
-        <v>46153</v>
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -10793,8 +11939,10 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
-        <v>46154</v>
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -10811,8 +11959,10 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
-        <v>46155</v>
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -10829,8 +11979,10 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
-        <v>46156</v>
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -10847,8 +11999,10 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
-        <v>46157</v>
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -10865,8 +12019,10 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
-        <v>46158</v>
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -10883,8 +12039,10 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
-        <v>46159</v>
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -10901,8 +12059,10 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
-        <v>46153</v>
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -10919,8 +12079,10 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
-        <v>46154</v>
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -10937,8 +12099,10 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
-        <v>46155</v>
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -10955,8 +12119,10 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
-        <v>46156</v>
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -10973,8 +12139,10 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
-        <v>46157</v>
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
@@ -10991,8 +12159,10 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
-        <v>46158</v>
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
@@ -11009,8 +12179,10 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
-        <v>46159</v>
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
@@ -11027,8 +12199,10 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
-        <v>46153</v>
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
@@ -11045,8 +12219,10 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
-        <v>46154</v>
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
@@ -11063,8 +12239,10 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
-        <v>46155</v>
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
@@ -11081,8 +12259,10 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
-        <v>46156</v>
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
@@ -11099,8 +12279,10 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
-        <v>46157</v>
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
@@ -11117,8 +12299,10 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
-        <v>46158</v>
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
@@ -11135,8 +12319,10 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
-        <v>46159</v>
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
@@ -11153,8 +12339,10 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
-        <v>46153</v>
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
@@ -11171,8 +12359,10 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
-        <v>46154</v>
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
@@ -11189,8 +12379,10 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
-        <v>46155</v>
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
@@ -11207,8 +12399,10 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
-        <v>46156</v>
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -11225,8 +12419,10 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
-        <v>46157</v>
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
@@ -11243,8 +12439,10 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
-        <v>46158</v>
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
@@ -11261,8 +12459,10 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="1" t="n">
-        <v>46159</v>
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
@@ -11279,8 +12479,10 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="1" t="n">
-        <v>46153</v>
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
@@ -11297,8 +12499,10 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="1" t="n">
-        <v>46154</v>
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
@@ -11315,8 +12519,10 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="1" t="n">
-        <v>46155</v>
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
@@ -11333,8 +12539,10 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="1" t="n">
-        <v>46156</v>
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
@@ -11351,8 +12559,10 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="1" t="n">
-        <v>46157</v>
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
@@ -11369,8 +12579,10 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="1" t="n">
-        <v>46158</v>
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
@@ -11387,8 +12599,10 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" s="1" t="n">
-        <v>46159</v>
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
@@ -11405,8 +12619,10 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="1" t="n">
-        <v>46153</v>
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
@@ -11423,8 +12639,10 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" s="1" t="n">
-        <v>46154</v>
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
@@ -11441,8 +12659,10 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" s="1" t="n">
-        <v>46155</v>
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
@@ -11459,8 +12679,10 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="1" t="n">
-        <v>46156</v>
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
@@ -11477,8 +12699,10 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" s="1" t="n">
-        <v>46157</v>
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
@@ -11495,8 +12719,10 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" s="1" t="n">
-        <v>46158</v>
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
@@ -11513,8 +12739,10 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" s="1" t="n">
-        <v>46159</v>
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
@@ -11531,8 +12759,10 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" s="1" t="n">
-        <v>46153</v>
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
@@ -11549,8 +12779,10 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" s="1" t="n">
-        <v>46154</v>
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
@@ -11567,8 +12799,10 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" s="1" t="n">
-        <v>46155</v>
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
@@ -11585,8 +12819,10 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="1" t="n">
-        <v>46156</v>
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
@@ -11603,8 +12839,10 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" s="1" t="n">
-        <v>46157</v>
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
@@ -11621,8 +12859,10 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" s="1" t="n">
-        <v>46158</v>
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
@@ -11639,8 +12879,10 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" s="1" t="n">
-        <v>46159</v>
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>

--- a/outputs/Tahminlenen_Talep.xlsx
+++ b/outputs/Tahminlenen_Talep.xlsx
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Cikis TM</t>
+          <t>Çıkış TM</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Varis TM</t>
+          <t>Varış TM</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
